--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="14400" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="301">
   <si>
     <t>id</t>
   </si>
@@ -885,6 +885,54 @@
   </si>
   <si>
     <t>HP Victus.webp</t>
+  </si>
+  <si>
+    <t>Acer Swift Lite 14</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 7 260</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pantautech.id/</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/LkuHe7M31</t>
+  </si>
+  <si>
+    <t>Acer Swift.webp</t>
+  </si>
+  <si>
+    <t>Acer Aspire 7 Pro</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7pqvDaEpiY</t>
+  </si>
+  <si>
+    <t>Acer 7.webp</t>
+  </si>
+  <si>
+    <t>Acer Aspire Go 14 Ai</t>
+  </si>
+  <si>
+    <t>Intel Ultra 7 115H</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/5fmQdwRw3n</t>
+  </si>
+  <si>
+    <t>Acer Go.webp</t>
+  </si>
+  <si>
+    <t>Axioo Pongo 750</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce RTX 4050 6GB</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/4qDJeZD73c</t>
+  </si>
+  <si>
+    <t>Axioo Pongo.webp</t>
   </si>
 </sst>
 </file>
@@ -897,7 +945,7 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -942,13 +990,6 @@
       <color rgb="FF1A5276"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1428,152 +1469,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1597,6 +1638,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1945,7 +1989,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3956,10 +4000,172 @@
         <v>284</v>
       </c>
     </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="3">
+        <v>206</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" s="3">
+        <v>12369000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="3">
+        <v>207</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="3">
+        <v>12316000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="3">
+        <v>208</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="3">
+        <v>11763000</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="3">
+        <v>209</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="3">
+        <v>12054000</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K57" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="I58" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
+    <hyperlink ref="I59" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
+    <hyperlink ref="I60" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
+    <hyperlink ref="I61" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12180"/>
+    <workbookView windowWidth="19200" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Products!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Products!$A$1:$K$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="315">
   <si>
     <t>id</t>
   </si>
@@ -893,46 +893,88 @@
     <t>AMD Ryzen 7 260</t>
   </si>
   <si>
+    <t>https://www.tiktok.com/@pantautech.id/photo/7651963993615092999</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/LkuHe7M31</t>
+  </si>
+  <si>
+    <t>Acer Swift.webp</t>
+  </si>
+  <si>
+    <t>Acer Aspire 7 Pro</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7pqvDaEpiY</t>
+  </si>
+  <si>
+    <t>Acer 7.webp</t>
+  </si>
+  <si>
+    <t>Acer Aspire Go 14 Ai</t>
+  </si>
+  <si>
+    <t>Intel Ultra 7 115H</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/5fmQdwRw3n</t>
+  </si>
+  <si>
+    <t>Acer Go.webp</t>
+  </si>
+  <si>
+    <t>Axioo Pongo 750</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce RTX 4050 6GB</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/4qDJeZD73c</t>
+  </si>
+  <si>
+    <t>Axioo Pongo.webp</t>
+  </si>
+  <si>
+    <t>Dell Latitude 7390</t>
+  </si>
+  <si>
+    <t>Intel Core i5 Gen 7</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@pantautech.id/</t>
   </si>
   <si>
-    <t>https://s.shopee.co.id/LkuHe7M31</t>
-  </si>
-  <si>
-    <t>Acer Swift.webp</t>
-  </si>
-  <si>
-    <t>Acer Aspire 7 Pro</t>
-  </si>
-  <si>
-    <t>https://s.shopee.co.id/7pqvDaEpiY</t>
-  </si>
-  <si>
-    <t>Acer 7.webp</t>
-  </si>
-  <si>
-    <t>Acer Aspire Go 14 Ai</t>
-  </si>
-  <si>
-    <t>Intel Ultra 7 115H</t>
-  </si>
-  <si>
-    <t>https://s.shopee.co.id/5fmQdwRw3n</t>
-  </si>
-  <si>
-    <t>Acer Go.webp</t>
-  </si>
-  <si>
-    <t>Axioo Pongo 750</t>
-  </si>
-  <si>
-    <t>Nvidia GeForce RTX 4050 6GB</t>
-  </si>
-  <si>
-    <t>https://s.shopee.co.id/4qDJeZD73c</t>
-  </si>
-  <si>
-    <t>Axioo Pongo.webp</t>
+    <t>https://s.shopee.co.id/4LH6HHflF4</t>
+  </si>
+  <si>
+    <t>Dell.webp</t>
+  </si>
+  <si>
+    <t>ThinkPad A485</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5 Pro 2500U</t>
+  </si>
+  <si>
+    <t>128GB</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/4Axg4ZK2vS</t>
+  </si>
+  <si>
+    <t>ThinkPad A.webp</t>
+  </si>
+  <si>
+    <t>ThinkPad X280</t>
+  </si>
+  <si>
+    <t>Intel Core i3-8</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/8pjVczxSba</t>
+  </si>
+  <si>
+    <t>ThinkPad X.webp</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1036,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1002,7 +1044,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1484,12 +1526,12 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1614,7 +1656,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1640,7 +1682,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1989,8 +2034,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -4060,7 +4105,7 @@
       <c r="H59" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I59" s="9" t="s">
+      <c r="I59" s="10" t="s">
         <v>287</v>
       </c>
       <c r="J59" s="3" t="s">
@@ -4095,7 +4140,7 @@
       <c r="H60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I60" s="9" t="s">
+      <c r="I60" s="10" t="s">
         <v>287</v>
       </c>
       <c r="J60" s="3" t="s">
@@ -4141,30 +4186,168 @@
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="3"/>
+      <c r="A62" s="3">
+        <v>210</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
+      <c r="A63" s="3">
+        <v>211</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="3">
+        <v>212</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" s="3">
+        <v>2700000</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K57" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="I58" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
-    <hyperlink ref="I59" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
-    <hyperlink ref="I60" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
-    <hyperlink ref="I61" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
+    <hyperlink ref="I62" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A586EE-6F4B-427D-98E7-53FD75B08CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -25,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="327">
   <si>
     <t>id</t>
   </si>
@@ -968,26 +977,56 @@
     <t>ThinkPad X280</t>
   </si>
   <si>
-    <t>Intel Core i3-8</t>
-  </si>
-  <si>
     <t>https://s.shopee.co.id/8pjVczxSba</t>
   </si>
   <si>
     <t>ThinkPad X.webp</t>
+  </si>
+  <si>
+    <t>Dell Latitude 7280</t>
+  </si>
+  <si>
+    <t>Intel Core i3 Gen 7</t>
+  </si>
+  <si>
+    <t>Intel Core i3 Gen 8</t>
+  </si>
+  <si>
+    <t>Intel Core i5 Gen 6</t>
+  </si>
+  <si>
+    <t>HP Probook 430 G3</t>
+  </si>
+  <si>
+    <t>ThinkPad T470</t>
+  </si>
+  <si>
+    <t>HP.webp</t>
+  </si>
+  <si>
+    <t>ThinkPad T.webp</t>
+  </si>
+  <si>
+    <t>Intel HD Graphics 520</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/Ll3prHAYI</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/5fmaCNUmww</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/9AMSPFvWZ5</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pantautech.id/photo/7653819332434070802</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1038,7 +1077,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1046,139 +1084,16 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1215,194 +1130,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1410,249 +1139,10 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1682,68 +1172,25 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2028,14 +1475,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -2044,13 +1491,13 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
     <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2085,7 +1532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:11">
+    <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2120,7 +1567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:11">
+    <row r="3" spans="1:11" ht="15.95" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2155,7 +1602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:11">
+    <row r="4" spans="1:11" ht="15.95" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2190,7 +1637,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:11">
+    <row r="5" spans="1:11" ht="15.95" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2225,7 +1672,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="1:11">
+    <row r="6" spans="1:11" ht="15.95" customHeight="1">
       <c r="A6" s="3">
         <v>80</v>
       </c>
@@ -2260,7 +1707,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="1:11">
+    <row r="7" spans="1:11" ht="15.95" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -2295,7 +1742,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" spans="1:11">
+    <row r="8" spans="1:11" ht="15.95" customHeight="1">
       <c r="A8" s="3">
         <v>10</v>
       </c>
@@ -2330,7 +1777,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="1:11">
+    <row r="9" spans="1:11" ht="15.95" customHeight="1">
       <c r="A9" s="3">
         <v>11</v>
       </c>
@@ -2365,7 +1812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="1:11">
+    <row r="10" spans="1:11" ht="15.95" customHeight="1">
       <c r="A10" s="3">
         <v>81</v>
       </c>
@@ -2400,7 +1847,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" spans="1:11">
+    <row r="11" spans="1:11" ht="15.95" customHeight="1">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -2435,7 +1882,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" spans="1:11">
+    <row r="12" spans="1:11" ht="15.95" customHeight="1">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -2470,7 +1917,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" spans="1:11">
+    <row r="13" spans="1:11" ht="15.95" customHeight="1">
       <c r="A13" s="5">
         <v>90</v>
       </c>
@@ -2505,7 +1952,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="15.95" customHeight="1">
       <c r="A14" s="5">
         <v>91</v>
       </c>
@@ -2540,7 +1987,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:11">
+    <row r="15" spans="1:11" ht="15.95" customHeight="1">
       <c r="A15" s="5">
         <v>92</v>
       </c>
@@ -2575,7 +2022,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" spans="1:11">
+    <row r="16" spans="1:11" ht="15.95" customHeight="1">
       <c r="A16" s="5">
         <v>6</v>
       </c>
@@ -2610,7 +2057,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" spans="1:11">
+    <row r="17" spans="1:11" ht="15.95" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -2645,7 +2092,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" spans="1:11">
+    <row r="18" spans="1:11" ht="15.95" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -2680,7 +2127,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" spans="1:11">
+    <row r="19" spans="1:11" ht="15.95" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2715,7 +2162,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" spans="1:11">
+    <row r="20" spans="1:11" ht="15.95" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2750,7 +2197,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" spans="1:11">
+    <row r="21" spans="1:11" ht="15.95" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2785,7 +2232,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" spans="1:11">
+    <row r="22" spans="1:11" ht="15.95" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2820,7 +2267,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" spans="1:11">
+    <row r="23" spans="1:11" ht="15.95" customHeight="1">
       <c r="A23" s="3">
         <v>83</v>
       </c>
@@ -2855,7 +2302,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:11">
+    <row r="24" spans="1:11" ht="15.95" customHeight="1">
       <c r="A24" s="5">
         <v>7</v>
       </c>
@@ -2890,7 +2337,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" spans="1:11">
+    <row r="25" spans="1:11" ht="15.95" customHeight="1">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -2925,7 +2372,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" spans="1:11">
+    <row r="26" spans="1:11" ht="15.95" customHeight="1">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -2960,7 +2407,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" spans="1:11">
+    <row r="27" spans="1:11" ht="15.95" customHeight="1">
       <c r="A27" s="7">
         <v>22</v>
       </c>
@@ -2995,7 +2442,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" spans="1:11">
+    <row r="28" spans="1:11" ht="15.95" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3030,7 +2477,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1" spans="1:11">
+    <row r="29" spans="1:11" ht="15.95" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -3065,7 +2512,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" spans="1:11">
+    <row r="30" spans="1:11" ht="15.95" customHeight="1">
       <c r="A30" s="5">
         <v>8</v>
       </c>
@@ -3100,7 +2547,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" spans="1:11">
+    <row r="31" spans="1:11" ht="15.95" customHeight="1">
       <c r="A31" s="7">
         <v>23</v>
       </c>
@@ -3135,7 +2582,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" spans="1:11">
+    <row r="32" spans="1:11" ht="15.95" customHeight="1">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -3170,7 +2617,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" spans="1:11">
+    <row r="33" spans="1:11" ht="15.95" customHeight="1">
       <c r="A33" s="7">
         <v>28</v>
       </c>
@@ -3205,7 +2652,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" spans="1:11">
+    <row r="34" spans="1:11" ht="15.95" customHeight="1">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -3240,7 +2687,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1" spans="1:11">
+    <row r="35" spans="1:11" ht="15.95" customHeight="1">
       <c r="A35" s="3">
         <v>30</v>
       </c>
@@ -3275,7 +2722,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1" spans="1:11">
+    <row r="36" spans="1:11" ht="15.95" customHeight="1">
       <c r="A36" s="3">
         <v>100</v>
       </c>
@@ -3310,7 +2757,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1" spans="1:11">
+    <row r="37" spans="1:11" ht="15.95" customHeight="1">
       <c r="A37" s="5">
         <v>9</v>
       </c>
@@ -3345,7 +2792,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1" spans="1:11">
+    <row r="38" spans="1:11" ht="15.95" customHeight="1">
       <c r="A38" s="5">
         <v>31</v>
       </c>
@@ -3380,7 +2827,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" spans="1:11">
+    <row r="39" spans="1:11" ht="15.95" customHeight="1">
       <c r="A39" s="7">
         <v>32</v>
       </c>
@@ -3415,7 +2862,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" spans="1:11">
+    <row r="40" spans="1:11" ht="15.95" customHeight="1">
       <c r="A40" s="7">
         <v>33</v>
       </c>
@@ -3450,7 +2897,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" spans="1:11">
+    <row r="41" spans="1:11" ht="15.95" customHeight="1">
       <c r="A41" s="7">
         <v>34</v>
       </c>
@@ -3485,7 +2932,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1" spans="1:11">
+    <row r="42" spans="1:11" ht="15.95" customHeight="1">
       <c r="A42" s="3">
         <v>36</v>
       </c>
@@ -3520,7 +2967,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1" spans="1:11">
+    <row r="43" spans="1:11" ht="15.95" customHeight="1">
       <c r="A43" s="7">
         <v>110</v>
       </c>
@@ -3555,7 +3002,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1" spans="1:11">
+    <row r="44" spans="1:11" ht="15.95" customHeight="1">
       <c r="A44" s="7">
         <v>120</v>
       </c>
@@ -3590,7 +3037,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1" spans="1:11">
+    <row r="45" spans="1:11" ht="15.95" customHeight="1">
       <c r="A45" s="7">
         <v>130</v>
       </c>
@@ -3625,7 +3072,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" spans="1:11">
+    <row r="46" spans="1:11" ht="15.95" customHeight="1">
       <c r="A46" s="7">
         <v>140</v>
       </c>
@@ -3660,7 +3107,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" spans="1:11">
+    <row r="47" spans="1:11" ht="15.95" customHeight="1">
       <c r="A47" s="5">
         <v>150</v>
       </c>
@@ -3695,7 +3142,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1" spans="1:11">
+    <row r="48" spans="1:11" ht="15.95" customHeight="1">
       <c r="A48" s="5">
         <v>160</v>
       </c>
@@ -3730,7 +3177,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1" spans="1:11">
+    <row r="49" spans="1:11" ht="15.95" customHeight="1">
       <c r="A49" s="3">
         <v>170</v>
       </c>
@@ -3765,7 +3212,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1" spans="1:11">
+    <row r="50" spans="1:11" ht="15.95" customHeight="1">
       <c r="A50" s="3">
         <v>180</v>
       </c>
@@ -3800,7 +3247,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1" spans="1:11">
+    <row r="51" spans="1:11" ht="15.95" customHeight="1">
       <c r="A51" s="7">
         <v>190</v>
       </c>
@@ -3835,7 +3282,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1" spans="1:11">
+    <row r="52" spans="1:11" ht="15.95" customHeight="1">
       <c r="A52" s="7">
         <v>200</v>
       </c>
@@ -3870,7 +3317,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1" spans="1:11">
+    <row r="53" spans="1:11" ht="15.95" customHeight="1">
       <c r="A53" s="7">
         <v>201</v>
       </c>
@@ -3905,7 +3352,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1" spans="1:11">
+    <row r="54" spans="1:11" ht="15.95" customHeight="1">
       <c r="A54" s="7">
         <v>202</v>
       </c>
@@ -3940,7 +3387,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1" spans="1:11">
+    <row r="55" spans="1:11" ht="15.95" customHeight="1">
       <c r="A55" s="7">
         <v>203</v>
       </c>
@@ -3975,7 +3422,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1" spans="1:11">
+    <row r="56" spans="1:11" ht="15.95" customHeight="1">
       <c r="A56" s="3">
         <v>204</v>
       </c>
@@ -4010,7 +3457,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1" spans="1:11">
+    <row r="57" spans="1:11" ht="15.95" customHeight="1">
       <c r="A57" s="3">
         <v>205</v>
       </c>
@@ -4211,7 +3658,7 @@
         <v>27</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>304</v>
@@ -4246,7 +3693,7 @@
         <v>308</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>309</v>
@@ -4269,7 +3716,7 @@
         <v>2700000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>32</v>
@@ -4281,75 +3728,123 @@
         <v>27</v>
       </c>
       <c r="I64" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="3">
+        <v>213</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1911000</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
+      <c r="J65" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
+      <c r="A66" s="3">
+        <v>214</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
+      <c r="A67" s="3">
+        <v>215</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>321</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K64" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <hyperlinks>
-    <hyperlink ref="I62" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/"/>
-  </hyperlinks>
+  <autoFilter ref="A1:K64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A586EE-6F4B-427D-98E7-53FD75B08CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236F590F-C199-47D2-ADB1-80C6E35BEFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="339">
   <si>
     <t>id</t>
   </si>
@@ -1020,6 +1020,42 @@
   </si>
   <si>
     <t>https://www.tiktok.com/@pantautech.id/photo/7653819332434070802</t>
+  </si>
+  <si>
+    <t>Asus Vivobook S14</t>
+  </si>
+  <si>
+    <t>Intel Ultra 5 225H</t>
+  </si>
+  <si>
+    <t>Acer Nitro Lite 16</t>
+  </si>
+  <si>
+    <t>Intel Core i5 210H</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 7-7840U</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/4VadxYRDTU</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7fXfiy6u9e</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7AbP7wO4xV</t>
+  </si>
+  <si>
+    <t>Asus.webp</t>
+  </si>
+  <si>
+    <t>Acer.webp</t>
+  </si>
+  <si>
+    <t>Intel Arc 130T</t>
+  </si>
+  <si>
+    <t>HP Pavilion Plus 14</t>
   </si>
 </sst>
 </file>
@@ -1481,8 +1517,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1491,13 +1527,13 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
     <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1">
+    <row r="1" spans="1:11" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1567,7 +1603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.95" customHeight="1">
+    <row r="3" spans="1:11" ht="16" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1602,7 +1638,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.95" customHeight="1">
+    <row r="4" spans="1:11" ht="16" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1637,7 +1673,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.95" customHeight="1">
+    <row r="5" spans="1:11" ht="16" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1672,7 +1708,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.95" customHeight="1">
+    <row r="6" spans="1:11" ht="16" customHeight="1">
       <c r="A6" s="3">
         <v>80</v>
       </c>
@@ -1707,7 +1743,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.95" customHeight="1">
+    <row r="7" spans="1:11" ht="16" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1742,7 +1778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.95" customHeight="1">
+    <row r="8" spans="1:11" ht="16" customHeight="1">
       <c r="A8" s="3">
         <v>10</v>
       </c>
@@ -1777,7 +1813,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.95" customHeight="1">
+    <row r="9" spans="1:11" ht="16" customHeight="1">
       <c r="A9" s="3">
         <v>11</v>
       </c>
@@ -1812,7 +1848,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.95" customHeight="1">
+    <row r="10" spans="1:11" ht="16" customHeight="1">
       <c r="A10" s="3">
         <v>81</v>
       </c>
@@ -1847,7 +1883,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.95" customHeight="1">
+    <row r="11" spans="1:11" ht="16" customHeight="1">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -1882,7 +1918,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.95" customHeight="1">
+    <row r="12" spans="1:11" ht="16" customHeight="1">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -1917,7 +1953,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.95" customHeight="1">
+    <row r="13" spans="1:11" ht="16" customHeight="1">
       <c r="A13" s="5">
         <v>90</v>
       </c>
@@ -1952,7 +1988,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.95" customHeight="1">
+    <row r="14" spans="1:11" ht="16" customHeight="1">
       <c r="A14" s="5">
         <v>91</v>
       </c>
@@ -1987,7 +2023,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.95" customHeight="1">
+    <row r="15" spans="1:11" ht="16" customHeight="1">
       <c r="A15" s="5">
         <v>92</v>
       </c>
@@ -2022,7 +2058,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.95" customHeight="1">
+    <row r="16" spans="1:11" ht="16" customHeight="1">
       <c r="A16" s="5">
         <v>6</v>
       </c>
@@ -2057,7 +2093,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.95" customHeight="1">
+    <row r="17" spans="1:11" ht="16" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -2092,7 +2128,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.95" customHeight="1">
+    <row r="18" spans="1:11" ht="16" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -2127,7 +2163,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.95" customHeight="1">
+    <row r="19" spans="1:11" ht="16" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2162,7 +2198,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.95" customHeight="1">
+    <row r="20" spans="1:11" ht="16" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2197,7 +2233,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.95" customHeight="1">
+    <row r="21" spans="1:11" ht="16" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2232,7 +2268,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.95" customHeight="1">
+    <row r="22" spans="1:11" ht="16" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2267,7 +2303,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.95" customHeight="1">
+    <row r="23" spans="1:11" ht="16" customHeight="1">
       <c r="A23" s="3">
         <v>83</v>
       </c>
@@ -2302,7 +2338,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.95" customHeight="1">
+    <row r="24" spans="1:11" ht="16" customHeight="1">
       <c r="A24" s="5">
         <v>7</v>
       </c>
@@ -2337,7 +2373,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.95" customHeight="1">
+    <row r="25" spans="1:11" ht="16" customHeight="1">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -2372,7 +2408,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.95" customHeight="1">
+    <row r="26" spans="1:11" ht="16" customHeight="1">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -2407,7 +2443,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.95" customHeight="1">
+    <row r="27" spans="1:11" ht="16" customHeight="1">
       <c r="A27" s="7">
         <v>22</v>
       </c>
@@ -2442,7 +2478,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.95" customHeight="1">
+    <row r="28" spans="1:11" ht="16" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2477,7 +2513,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.95" customHeight="1">
+    <row r="29" spans="1:11" ht="16" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -2512,7 +2548,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.95" customHeight="1">
+    <row r="30" spans="1:11" ht="16" customHeight="1">
       <c r="A30" s="5">
         <v>8</v>
       </c>
@@ -2547,7 +2583,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.95" customHeight="1">
+    <row r="31" spans="1:11" ht="16" customHeight="1">
       <c r="A31" s="7">
         <v>23</v>
       </c>
@@ -2582,7 +2618,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.95" customHeight="1">
+    <row r="32" spans="1:11" ht="16" customHeight="1">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -2617,7 +2653,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.95" customHeight="1">
+    <row r="33" spans="1:11" ht="16" customHeight="1">
       <c r="A33" s="7">
         <v>28</v>
       </c>
@@ -2652,7 +2688,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.95" customHeight="1">
+    <row r="34" spans="1:11" ht="16" customHeight="1">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2687,7 +2723,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15.95" customHeight="1">
+    <row r="35" spans="1:11" ht="16" customHeight="1">
       <c r="A35" s="3">
         <v>30</v>
       </c>
@@ -2722,7 +2758,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.95" customHeight="1">
+    <row r="36" spans="1:11" ht="16" customHeight="1">
       <c r="A36" s="3">
         <v>100</v>
       </c>
@@ -2757,7 +2793,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.95" customHeight="1">
+    <row r="37" spans="1:11" ht="16" customHeight="1">
       <c r="A37" s="5">
         <v>9</v>
       </c>
@@ -2792,7 +2828,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.95" customHeight="1">
+    <row r="38" spans="1:11" ht="16" customHeight="1">
       <c r="A38" s="5">
         <v>31</v>
       </c>
@@ -2827,7 +2863,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.95" customHeight="1">
+    <row r="39" spans="1:11" ht="16" customHeight="1">
       <c r="A39" s="7">
         <v>32</v>
       </c>
@@ -2862,7 +2898,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.95" customHeight="1">
+    <row r="40" spans="1:11" ht="16" customHeight="1">
       <c r="A40" s="7">
         <v>33</v>
       </c>
@@ -2897,7 +2933,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15.95" customHeight="1">
+    <row r="41" spans="1:11" ht="16" customHeight="1">
       <c r="A41" s="7">
         <v>34</v>
       </c>
@@ -2932,7 +2968,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15.95" customHeight="1">
+    <row r="42" spans="1:11" ht="16" customHeight="1">
       <c r="A42" s="3">
         <v>36</v>
       </c>
@@ -2967,7 +3003,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15.95" customHeight="1">
+    <row r="43" spans="1:11" ht="16" customHeight="1">
       <c r="A43" s="7">
         <v>110</v>
       </c>
@@ -3002,7 +3038,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15.95" customHeight="1">
+    <row r="44" spans="1:11" ht="16" customHeight="1">
       <c r="A44" s="7">
         <v>120</v>
       </c>
@@ -3037,7 +3073,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15.95" customHeight="1">
+    <row r="45" spans="1:11" ht="16" customHeight="1">
       <c r="A45" s="7">
         <v>130</v>
       </c>
@@ -3072,7 +3108,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15.95" customHeight="1">
+    <row r="46" spans="1:11" ht="16" customHeight="1">
       <c r="A46" s="7">
         <v>140</v>
       </c>
@@ -3107,7 +3143,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15.95" customHeight="1">
+    <row r="47" spans="1:11" ht="16" customHeight="1">
       <c r="A47" s="5">
         <v>150</v>
       </c>
@@ -3142,7 +3178,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.95" customHeight="1">
+    <row r="48" spans="1:11" ht="16" customHeight="1">
       <c r="A48" s="5">
         <v>160</v>
       </c>
@@ -3177,7 +3213,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15.95" customHeight="1">
+    <row r="49" spans="1:11" ht="16" customHeight="1">
       <c r="A49" s="3">
         <v>170</v>
       </c>
@@ -3212,7 +3248,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15.95" customHeight="1">
+    <row r="50" spans="1:11" ht="16" customHeight="1">
       <c r="A50" s="3">
         <v>180</v>
       </c>
@@ -3247,7 +3283,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.95" customHeight="1">
+    <row r="51" spans="1:11" ht="16" customHeight="1">
       <c r="A51" s="7">
         <v>190</v>
       </c>
@@ -3282,7 +3318,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.95" customHeight="1">
+    <row r="52" spans="1:11" ht="16" customHeight="1">
       <c r="A52" s="7">
         <v>200</v>
       </c>
@@ -3317,7 +3353,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.95" customHeight="1">
+    <row r="53" spans="1:11" ht="16" customHeight="1">
       <c r="A53" s="7">
         <v>201</v>
       </c>
@@ -3352,7 +3388,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15.95" customHeight="1">
+    <row r="54" spans="1:11" ht="16" customHeight="1">
       <c r="A54" s="7">
         <v>202</v>
       </c>
@@ -3387,7 +3423,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.95" customHeight="1">
+    <row r="55" spans="1:11" ht="16" customHeight="1">
       <c r="A55" s="7">
         <v>203</v>
       </c>
@@ -3422,7 +3458,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.95" customHeight="1">
+    <row r="56" spans="1:11" ht="16" customHeight="1">
       <c r="A56" s="3">
         <v>204</v>
       </c>
@@ -3457,7 +3493,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.95" customHeight="1">
+    <row r="57" spans="1:11" ht="16" customHeight="1">
       <c r="A57" s="3">
         <v>205</v>
       </c>
@@ -3841,6 +3877,527 @@
       <c r="K67" s="3" t="s">
         <v>321</v>
       </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="3">
+        <v>216</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" s="3">
+        <v>13014000</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="3">
+        <v>217</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="3">
+        <v>12926000</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="3">
+        <v>218</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" s="3">
+        <v>13994000</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="10"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="10"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="10"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="10"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="10"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="10"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236F590F-C199-47D2-ADB1-80C6E35BEFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0693602-2510-4451-927E-E8856C20B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="359">
   <si>
     <t>id</t>
   </si>
@@ -1056,13 +1056,73 @@
   </si>
   <si>
     <t>HP Pavilion Plus 14</t>
+  </si>
+  <si>
+    <t>MSI Thin 15 B13VE-3415</t>
+  </si>
+  <si>
+    <t>Acer Nitro Lite 16 NL16</t>
+  </si>
+  <si>
+    <t>HP Omnibook 3 Ai 14</t>
+  </si>
+  <si>
+    <t>Intel Ultra 5 325</t>
+  </si>
+  <si>
+    <t>MSI Modern 15 C2RMG</t>
+  </si>
+  <si>
+    <t>Intel Core 9 270H</t>
+  </si>
+  <si>
+    <t>Asus Zenbook 14 OLED</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 7 8840HS</t>
+  </si>
+  <si>
+    <t>Intel Xe3</t>
+  </si>
+  <si>
+    <t>Intel Iris Xe G7 96EU</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pantautech.id/photo/7654187844063333639</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pantautech.id/photo/7654537785574984978</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/1gGZItsz7U</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/60PYT4kR6g</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/70I5f17yL5</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/9zvhEbMMhY</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/2LWG6YWjzk</t>
+  </si>
+  <si>
+    <t>MSIT.webp</t>
+  </si>
+  <si>
+    <t>MSIM.webp</t>
+  </si>
+  <si>
+    <t>HP Omni.webp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1128,6 +1188,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1182,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1212,6 +1278,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3799,7 +3868,7 @@
         <v>27</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>323</v>
@@ -3834,7 +3903,7 @@
         <v>308</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>324</v>
@@ -3869,7 +3938,7 @@
         <v>308</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>325</v>
@@ -3904,7 +3973,7 @@
         <v>221</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>334</v>
@@ -3939,7 +4008,7 @@
         <v>59</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>333</v>
@@ -3974,7 +4043,7 @@
         <v>221</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>332</v>
@@ -3984,69 +4053,179 @@
       </c>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
+      <c r="A71" s="3">
+        <v>219</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="3">
+        <v>13994000</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+      <c r="A72" s="3">
+        <v>220</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D72" s="3">
+        <v>14149000</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="A73" s="3">
+        <v>221</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="3">
+        <v>14494000</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
+      <c r="A74" s="3">
+        <v>222</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D74" s="3">
+        <v>14446000</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
+      <c r="A75" s="3">
+        <v>223</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" s="3">
+        <v>14274000</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="3"/>
@@ -4402,6 +4581,14 @@
   </sheetData>
   <autoFilter ref="A1:K64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I71" r:id="rId1" xr:uid="{6F1E8E2A-F0B2-4FF0-BC74-4A8121683576}"/>
+    <hyperlink ref="I73" r:id="rId2" xr:uid="{F4A809E4-AE97-49E2-A956-EA001BCB01B4}"/>
+    <hyperlink ref="I75" r:id="rId3" xr:uid="{E3C64849-92F0-45BB-8BCD-5972CEFA270E}"/>
+    <hyperlink ref="I72" r:id="rId4" xr:uid="{6F2A78C6-8FA8-4463-ACC7-363DD6C98B8D}"/>
+    <hyperlink ref="I74" r:id="rId5" xr:uid="{F0589B13-1C16-42C3-8135-EB4A5A6E5481}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0693602-2510-4451-927E-E8856C20B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6741925-C114-4ADB-A31F-E98F9F4A20FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="370">
   <si>
     <t>id</t>
   </si>
@@ -209,9 +209,6 @@
     <t>Dell Latitude 7410.webp</t>
   </si>
   <si>
-    <t>HP Elitebook 845 G8</t>
-  </si>
-  <si>
     <t>AMD Ryzen 5 Pro 5650U</t>
   </si>
   <si>
@@ -398,9 +395,6 @@
     <t>HP Elitebook 835 G8.webp</t>
   </si>
   <si>
-    <t>ThinkPad T14 Gen 2 AMD</t>
-  </si>
-  <si>
     <t>https://s.shopee.co.id/3VhpKL328P</t>
   </si>
   <si>
@@ -1116,13 +1110,52 @@
   </si>
   <si>
     <t>HP Omni.webp</t>
+  </si>
+  <si>
+    <t>Intel Core i5 Gen 8</t>
+  </si>
+  <si>
+    <t>ThinkPad T14 Gen 2 Ryzen 7</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/9fIsAZatzM</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7VENaYDr4J</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/4AxvbMQSix</t>
+  </si>
+  <si>
+    <t>dell 5400.webp</t>
+  </si>
+  <si>
+    <t>thinkpad t.webp</t>
+  </si>
+  <si>
+    <t>thinkpad x.webp</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@pantautech.id/photo/7656043970857913618</t>
+  </si>
+  <si>
+    <t>ThinkPad T14 Gen 2 Ryzen 5 (TERLARIS)</t>
+  </si>
+  <si>
+    <t>ThinkPad X390 (TERLARIS)</t>
+  </si>
+  <si>
+    <t>Dell Latitude 5400 (TERLARIS)</t>
+  </si>
+  <si>
+    <t>HP Elitebook 845 G8 (TERLARIS)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,6 +1227,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7D6608"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1248,7 +1287,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1281,6 +1320,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1587,7 +1629,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1596,13 +1638,13 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
     <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22" customHeight="1">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1672,7 +1714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1">
+    <row r="3" spans="1:11" ht="15.95" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1707,7 +1749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16" customHeight="1">
+    <row r="4" spans="1:11" ht="15.95" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1742,7 +1784,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16" customHeight="1">
+    <row r="5" spans="1:11" ht="15.95" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1777,7 +1819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" customHeight="1">
+    <row r="6" spans="1:11" ht="15.95" customHeight="1">
       <c r="A6" s="3">
         <v>80</v>
       </c>
@@ -1812,7 +1854,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16" customHeight="1">
+    <row r="7" spans="1:11" ht="15.95" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1847,7 +1889,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" customHeight="1">
+    <row r="8" spans="1:11" ht="15.95" customHeight="1">
       <c r="A8" s="3">
         <v>10</v>
       </c>
@@ -1882,47 +1924,47 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16" customHeight="1">
+    <row r="9" spans="1:11" ht="15.95" customHeight="1">
       <c r="A9" s="3">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>369</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>4991000</v>
+        <v>5509000</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="10" spans="1:11" ht="15.95" customHeight="1">
       <c r="A10" s="3">
         <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
@@ -1931,10 +1973,10 @@
         <v>4883000</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>41</v>
@@ -1946,18 +1988,18 @@
         <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="11" spans="1:11" ht="15.95" customHeight="1">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
@@ -1966,33 +2008,33 @@
         <v>5424000</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="12" spans="1:11" ht="15.95" customHeight="1">
       <c r="A12" s="3">
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>23</v>
@@ -2001,45 +2043,45 @@
         <v>5664000</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="13" spans="1:11" ht="15.95" customHeight="1">
       <c r="A13" s="5">
         <v>90</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="D13" s="5">
         <v>5951000</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>41</v>
@@ -2048,33 +2090,33 @@
         <v>27</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="14" spans="1:11" ht="15.95" customHeight="1">
       <c r="A14" s="5">
         <v>91</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="5">
         <v>5759000</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>41</v>
@@ -2083,33 +2125,33 @@
         <v>27</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="15" spans="1:11" ht="15.95" customHeight="1">
       <c r="A15" s="5">
         <v>92</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="5">
         <v>5466000</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>41</v>
@@ -2118,33 +2160,33 @@
         <v>27</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="16" spans="1:11" ht="15.95" customHeight="1">
       <c r="A16" s="5">
         <v>6</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="5">
         <v>6788000</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>41</v>
@@ -2153,68 +2195,68 @@
         <v>27</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="17" spans="1:11" ht="15.95" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" s="5">
         <v>6620000</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="18" spans="1:11" ht="15.95" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" s="5">
         <v>6881000</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>41</v>
@@ -2223,33 +2265,33 @@
         <v>27</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="19" spans="1:11" ht="15.95" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="D19" s="7">
         <v>6416000</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>41</v>
@@ -2258,21 +2300,21 @@
         <v>27</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="20" spans="1:11" ht="15.95" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>23</v>
@@ -2281,33 +2323,33 @@
         <v>6958000</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="21" spans="1:11" ht="15.95" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>119</v>
+      <c r="B21" s="11" t="s">
+        <v>358</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
@@ -2316,10 +2358,10 @@
         <v>6240000</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -2328,21 +2370,21 @@
         <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="16" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.95" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>23</v>
@@ -2351,10 +2393,10 @@
         <v>6912000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>26</v>
@@ -2363,21 +2405,21 @@
         <v>27</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="16" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.95" customHeight="1">
       <c r="A23" s="3">
         <v>83</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>23</v>
@@ -2386,10 +2428,10 @@
         <v>6993000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>26</v>
@@ -2401,30 +2443,30 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="16" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.95" customHeight="1">
       <c r="A24" s="5">
         <v>7</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="5">
         <v>7391000</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>41</v>
@@ -2433,68 +2475,68 @@
         <v>27</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="25" spans="1:11" ht="15.95" customHeight="1">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="5">
         <v>7434000</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="16" customHeight="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.95" customHeight="1">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" s="5">
         <v>7583000</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>41</v>
@@ -2503,33 +2545,33 @@
         <v>27</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="16" customHeight="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.95" customHeight="1">
       <c r="A27" s="7">
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" s="7">
         <v>7949000</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>41</v>
@@ -2538,21 +2580,21 @@
         <v>27</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="16" customHeight="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.95" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
@@ -2561,45 +2603,45 @@
         <v>7500000</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="16" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.95" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D29" s="5">
         <v>7871000</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>41</v>
@@ -2608,33 +2650,33 @@
         <v>27</v>
       </c>
       <c r="I29" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="J29" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="30" spans="1:11" ht="15.95" customHeight="1">
       <c r="A30" s="5">
         <v>8</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" s="5">
         <v>8207000</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>41</v>
@@ -2643,161 +2685,161 @@
         <v>27</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="16" customHeight="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.95" customHeight="1">
       <c r="A31" s="7">
         <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D31" s="7">
         <v>8201000</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="16" customHeight="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.95" customHeight="1">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="5">
         <v>8364000</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="16" customHeight="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.95" customHeight="1">
       <c r="A33" s="7">
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D33" s="7">
         <v>8062000</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="16" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.95" customHeight="1">
       <c r="A34" s="7">
         <v>29</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" s="7">
         <v>8099000</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="16" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.95" customHeight="1">
       <c r="A35" s="3">
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
@@ -2806,10 +2848,10 @@
         <v>8544000</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>26</v>
@@ -2818,21 +2860,21 @@
         <v>27</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="16" customHeight="1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.95" customHeight="1">
       <c r="A36" s="3">
         <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>23</v>
@@ -2841,10 +2883,10 @@
         <v>8544000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>26</v>
@@ -2853,68 +2895,68 @@
         <v>27</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="16" customHeight="1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15.95" customHeight="1">
       <c r="A37" s="5">
         <v>9</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" s="5">
         <v>9599000</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K37" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="38" spans="1:11" ht="15.95" customHeight="1">
       <c r="A38" s="5">
         <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="5">
         <v>9599000</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>41</v>
@@ -2923,126 +2965,126 @@
         <v>27</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="16" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15.95" customHeight="1">
       <c r="A39" s="7">
         <v>32</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" s="7">
         <v>9205000</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="16" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.95" customHeight="1">
       <c r="A40" s="7">
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D40" s="7">
         <v>9159000</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="16" customHeight="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.95" customHeight="1">
       <c r="A41" s="7">
         <v>34</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D41" s="7">
         <v>9119000</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="16" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.95" customHeight="1">
       <c r="A42" s="3">
         <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -3051,243 +3093,243 @@
         <v>9312000</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="16" customHeight="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.95" customHeight="1">
       <c r="A43" s="7">
         <v>110</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D43" s="7">
         <v>10182000</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I43" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="K43" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="J43" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="44" spans="1:11" ht="15.95" customHeight="1">
       <c r="A44" s="7">
         <v>120</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="7">
         <v>10463000</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="K44" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I44" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="45" spans="1:11" ht="15.95" customHeight="1">
       <c r="A45" s="7">
         <v>130</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" s="7">
         <v>10224000</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="16" customHeight="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.95" customHeight="1">
       <c r="A46" s="7">
         <v>140</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" s="7">
         <v>10284000</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="16" customHeight="1">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15.95" customHeight="1">
       <c r="A47" s="5">
         <v>150</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" s="5">
         <v>10224000</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="16" customHeight="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15.95" customHeight="1">
       <c r="A48" s="5">
         <v>160</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" s="5">
         <v>10128000</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="16" customHeight="1">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15.95" customHeight="1">
       <c r="A49" s="3">
         <v>170</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>23</v>
@@ -3296,10 +3338,10 @@
         <v>10464000</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>26</v>
@@ -3308,21 +3350,21 @@
         <v>27</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="16" customHeight="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15.95" customHeight="1">
       <c r="A50" s="3">
         <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -3331,208 +3373,208 @@
         <v>10224000</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="16" customHeight="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15.95" customHeight="1">
       <c r="A51" s="7">
         <v>190</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D51" s="7">
         <v>11138000</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I51" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="J51" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="16" customHeight="1">
+    </row>
+    <row r="52" spans="1:11" ht="15.95" customHeight="1">
       <c r="A52" s="7">
         <v>200</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D52" s="7">
         <v>11553000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="16" customHeight="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.95" customHeight="1">
       <c r="A53" s="7">
         <v>201</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D53" s="7">
         <v>10880000</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="16" customHeight="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.95" customHeight="1">
       <c r="A54" s="7">
         <v>202</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D54" s="7">
         <v>11399000</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="16" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15.95" customHeight="1">
       <c r="A55" s="7">
         <v>203</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="7">
         <v>12042000</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="16" customHeight="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15.95" customHeight="1">
       <c r="A56" s="3">
         <v>204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -3541,10 +3583,10 @@
         <v>11564000</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>26</v>
@@ -3553,21 +3595,21 @@
         <v>27</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16" customHeight="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15.95" customHeight="1">
       <c r="A57" s="3">
         <v>205</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>23</v>
@@ -3576,25 +3618,25 @@
         <v>11956000</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3602,34 +3644,34 @@
         <v>206</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D58" s="3">
         <v>12369000</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I58" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3637,34 +3679,34 @@
         <v>207</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D59" s="3">
         <v>12316000</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3672,34 +3714,34 @@
         <v>208</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D60" s="3">
         <v>11763000</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3707,7 +3749,7 @@
         <v>209</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>23</v>
@@ -3716,25 +3758,25 @@
         <v>12054000</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3742,7 +3784,7 @@
         <v>210</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>23</v>
@@ -3751,7 +3793,7 @@
         <v>2850000</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>32</v>
@@ -3763,13 +3805,13 @@
         <v>27</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3777,7 +3819,7 @@
         <v>211</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>23</v>
@@ -3786,25 +3828,25 @@
         <v>2900000</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3812,7 +3854,7 @@
         <v>212</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>23</v>
@@ -3821,7 +3863,7 @@
         <v>2700000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>32</v>
@@ -3833,13 +3875,13 @@
         <v>27</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3847,7 +3889,7 @@
         <v>213</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -3856,7 +3898,7 @@
         <v>1911000</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>32</v>
@@ -3868,13 +3910,13 @@
         <v>27</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3882,7 +3924,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -3891,25 +3933,25 @@
         <v>1860000</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3917,7 +3959,7 @@
         <v>215</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -3926,7 +3968,7 @@
         <v>1875000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>32</v>
@@ -3935,16 +3977,16 @@
         <v>41</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3952,34 +3994,34 @@
         <v>216</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D68" s="3">
         <v>13014000</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3987,34 +4029,34 @@
         <v>217</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D69" s="3">
         <v>12926000</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4022,34 +4064,34 @@
         <v>218</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D70" s="3">
         <v>13994000</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4057,34 +4099,34 @@
         <v>219</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D71" s="3">
         <v>13994000</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4092,34 +4134,34 @@
         <v>220</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="3">
         <v>14149000</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4127,34 +4169,34 @@
         <v>221</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D73" s="3">
         <v>14494000</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4162,34 +4204,34 @@
         <v>222</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D74" s="3">
         <v>14446000</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4197,74 +4239,140 @@
         <v>223</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D75" s="3">
         <v>14274000</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
+      <c r="A76" s="3">
+        <v>224</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
+      <c r="A77" s="3">
+        <v>225</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="3">
+        <v>5520000</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
+      <c r="A78" s="3">
+        <v>226</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="3"/>
@@ -4582,13 +4690,9 @@
   <autoFilter ref="A1:K64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I71" r:id="rId1" xr:uid="{6F1E8E2A-F0B2-4FF0-BC74-4A8121683576}"/>
-    <hyperlink ref="I73" r:id="rId2" xr:uid="{F4A809E4-AE97-49E2-A956-EA001BCB01B4}"/>
-    <hyperlink ref="I75" r:id="rId3" xr:uid="{E3C64849-92F0-45BB-8BCD-5972CEFA270E}"/>
-    <hyperlink ref="I72" r:id="rId4" xr:uid="{6F2A78C6-8FA8-4463-ACC7-363DD6C98B8D}"/>
-    <hyperlink ref="I74" r:id="rId5" xr:uid="{F0589B13-1C16-42C3-8135-EB4A5A6E5481}"/>
+    <hyperlink ref="I76:I78" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/" xr:uid="{7A9DFC0A-9F74-45F0-B51F-2573F164C957}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6741925-C114-4ADB-A31F-E98F9F4A20FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6710B9B8-7790-4689-B288-AF8BB31FFC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="395">
   <si>
     <t>id</t>
   </si>
@@ -596,9 +596,6 @@
     <t>https://s.shopee.co.id/902mDBFWzY</t>
   </si>
   <si>
-    <t>Advan Pixwar (GAMING)</t>
-  </si>
-  <si>
     <t>AMD Ryzen 7 8745HS</t>
   </si>
   <si>
@@ -773,9 +770,6 @@
     <t>ThinkPad P1 G2.webp</t>
   </si>
   <si>
-    <t>Lenovo Legion 5 15ARH05H</t>
-  </si>
-  <si>
     <t>AMD Ryzen 5 4600H</t>
   </si>
   <si>
@@ -830,9 +824,6 @@
     <t>HP Omnibook.webp</t>
   </si>
   <si>
-    <t>MSI Thin 15 B12UC-3298</t>
-  </si>
-  <si>
     <t>Intel Core i7-12650H</t>
   </si>
   <si>
@@ -845,9 +836,6 @@
     <t>MSI Thin.webp</t>
   </si>
   <si>
-    <t>Lenovo LOQ Essential 15ARP10E</t>
-  </si>
-  <si>
     <t>AMD Ryzen 7 7735HS</t>
   </si>
   <si>
@@ -875,9 +863,6 @@
     <t>ThinkPad P53.webp</t>
   </si>
   <si>
-    <t>HP Victus 16</t>
-  </si>
-  <si>
     <t>Intel Core i7-12700H</t>
   </si>
   <si>
@@ -905,9 +890,6 @@
     <t>Acer Swift.webp</t>
   </si>
   <si>
-    <t>Acer Aspire 7 Pro</t>
-  </si>
-  <si>
     <t>https://s.shopee.co.id/7pqvDaEpiY</t>
   </si>
   <si>
@@ -926,9 +908,6 @@
     <t>Acer Go.webp</t>
   </si>
   <si>
-    <t>Axioo Pongo 750</t>
-  </si>
-  <si>
     <t>Nvidia GeForce RTX 4050 6GB</t>
   </si>
   <si>
@@ -1022,9 +1001,6 @@
     <t>Intel Ultra 5 225H</t>
   </si>
   <si>
-    <t>Acer Nitro Lite 16</t>
-  </si>
-  <si>
     <t>Intel Core i5 210H</t>
   </si>
   <si>
@@ -1052,12 +1028,6 @@
     <t>HP Pavilion Plus 14</t>
   </si>
   <si>
-    <t>MSI Thin 15 B13VE-3415</t>
-  </si>
-  <si>
-    <t>Acer Nitro Lite 16 NL16</t>
-  </si>
-  <si>
     <t>HP Omnibook 3 Ai 14</t>
   </si>
   <si>
@@ -1149,6 +1119,111 @@
   </si>
   <si>
     <t>HP Elitebook 845 G8 (TERLARIS)</t>
+  </si>
+  <si>
+    <t>Asus TUF FX504GE (GAMING)</t>
+  </si>
+  <si>
+    <t>Intel Core i7-8750H</t>
+  </si>
+  <si>
+    <t>SSD 256GB,HDD 1TB</t>
+  </si>
+  <si>
+    <t>Asus TUF FX505GT (GAMING)</t>
+  </si>
+  <si>
+    <t>Intel Core i5-9300H</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce GTX 1050Ti 4GB</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce GTX 1650 4GB</t>
+  </si>
+  <si>
+    <t>MSI GF63 Thin 9SCSR (GAMING)</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce GTX 1650Ti 4GB</t>
+  </si>
+  <si>
+    <t>SSD 512GB,HDD 500GB</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5 5500H</t>
+  </si>
+  <si>
+    <t>Nvidia GeForce RTX 2050 4GB</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5 5600H</t>
+  </si>
+  <si>
+    <t>tuf 1.webp</t>
+  </si>
+  <si>
+    <t>tuf 2.webp</t>
+  </si>
+  <si>
+    <t>msi.webp</t>
+  </si>
+  <si>
+    <t>lenovoig2.webp</t>
+  </si>
+  <si>
+    <t>lenovoig1.webp</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7AbXWXHtnA</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/8fQLJUKXYW</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/5q69wSojoS</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/6L2QXXGXaG</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/7VENvvWMxk</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Gaming 3 2050 (GAMING)</t>
+  </si>
+  <si>
+    <t>Lenovo Ideapad Gaming 3 3060 (GAMING)</t>
+  </si>
+  <si>
+    <t>MSI Thin 15 B12UC-3298 (GAMING)</t>
+  </si>
+  <si>
+    <t>Lenovo LOQ Essential 15ARP10E (GAMING)</t>
+  </si>
+  <si>
+    <t>HP Victus 16 (GAMING)</t>
+  </si>
+  <si>
+    <t>Acer Aspire 7 Pro (GAMING)</t>
+  </si>
+  <si>
+    <t>Axioo Pongo 750 (GAMING)</t>
+  </si>
+  <si>
+    <t>Acer Nitro Lite 16 (GAMING)</t>
+  </si>
+  <si>
+    <t>MSI Thin 15 B13VE-3415 (GAMING)</t>
+  </si>
+  <si>
+    <t>Acer Nitro Lite 16 NL16 (GAMING)</t>
+  </si>
+  <si>
+    <t>Lenovo Legion 5 15ARH05H (GAMING)</t>
+  </si>
+  <si>
+    <t>Advan Pixwar</t>
   </si>
 </sst>
 </file>
@@ -1629,22 +1704,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="37.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
     <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1">
+    <row r="1" spans="1:11" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1714,7 +1789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.95" customHeight="1">
+    <row r="3" spans="1:11" ht="16" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1749,7 +1824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.95" customHeight="1">
+    <row r="4" spans="1:11" ht="16" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1784,7 +1859,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.95" customHeight="1">
+    <row r="5" spans="1:11" ht="16" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1819,7 +1894,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.95" customHeight="1">
+    <row r="6" spans="1:11" ht="16" customHeight="1">
       <c r="A6" s="3">
         <v>80</v>
       </c>
@@ -1854,7 +1929,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.95" customHeight="1">
+    <row r="7" spans="1:11" ht="16" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1889,7 +1964,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.95" customHeight="1">
+    <row r="8" spans="1:11" ht="16" customHeight="1">
       <c r="A8" s="3">
         <v>10</v>
       </c>
@@ -1924,12 +1999,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.95" customHeight="1">
+    <row r="9" spans="1:11" ht="16" customHeight="1">
       <c r="A9" s="3">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>23</v>
@@ -1959,7 +2034,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.95" customHeight="1">
+    <row r="10" spans="1:11" ht="16" customHeight="1">
       <c r="A10" s="3">
         <v>81</v>
       </c>
@@ -1994,7 +2069,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.95" customHeight="1">
+    <row r="11" spans="1:11" ht="16" customHeight="1">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -2029,7 +2104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.95" customHeight="1">
+    <row r="12" spans="1:11" ht="16" customHeight="1">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -2064,7 +2139,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.95" customHeight="1">
+    <row r="13" spans="1:11" ht="16" customHeight="1">
       <c r="A13" s="5">
         <v>90</v>
       </c>
@@ -2099,7 +2174,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.95" customHeight="1">
+    <row r="14" spans="1:11" ht="16" customHeight="1">
       <c r="A14" s="5">
         <v>91</v>
       </c>
@@ -2134,7 +2209,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.95" customHeight="1">
+    <row r="15" spans="1:11" ht="16" customHeight="1">
       <c r="A15" s="5">
         <v>92</v>
       </c>
@@ -2169,7 +2244,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.95" customHeight="1">
+    <row r="16" spans="1:11" ht="16" customHeight="1">
       <c r="A16" s="5">
         <v>6</v>
       </c>
@@ -2204,7 +2279,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.95" customHeight="1">
+    <row r="17" spans="1:11" ht="16" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -2239,7 +2314,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.95" customHeight="1">
+    <row r="18" spans="1:11" ht="16" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -2274,7 +2349,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.95" customHeight="1">
+    <row r="19" spans="1:11" ht="16" customHeight="1">
       <c r="A19" s="7">
         <v>16</v>
       </c>
@@ -2309,7 +2384,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.95" customHeight="1">
+    <row r="20" spans="1:11" ht="16" customHeight="1">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -2344,12 +2419,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.95" customHeight="1">
+    <row r="21" spans="1:11" ht="16" customHeight="1">
       <c r="A21" s="3">
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
@@ -2379,7 +2454,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.95" customHeight="1">
+    <row r="22" spans="1:11" ht="16" customHeight="1">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2414,7 +2489,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.95" customHeight="1">
+    <row r="23" spans="1:11" ht="16" customHeight="1">
       <c r="A23" s="3">
         <v>83</v>
       </c>
@@ -2449,7 +2524,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.95" customHeight="1">
+    <row r="24" spans="1:11" ht="16" customHeight="1">
       <c r="A24" s="5">
         <v>7</v>
       </c>
@@ -2484,7 +2559,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.95" customHeight="1">
+    <row r="25" spans="1:11" ht="16" customHeight="1">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -2519,7 +2594,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.95" customHeight="1">
+    <row r="26" spans="1:11" ht="16" customHeight="1">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -2554,7 +2629,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.95" customHeight="1">
+    <row r="27" spans="1:11" ht="16" customHeight="1">
       <c r="A27" s="7">
         <v>22</v>
       </c>
@@ -2589,7 +2664,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.95" customHeight="1">
+    <row r="28" spans="1:11" ht="16" customHeight="1">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2624,7 +2699,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.95" customHeight="1">
+    <row r="29" spans="1:11" ht="16" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -2659,7 +2734,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.95" customHeight="1">
+    <row r="30" spans="1:11" ht="16" customHeight="1">
       <c r="A30" s="5">
         <v>8</v>
       </c>
@@ -2694,7 +2769,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.95" customHeight="1">
+    <row r="31" spans="1:11" ht="16" customHeight="1">
       <c r="A31" s="7">
         <v>23</v>
       </c>
@@ -2729,7 +2804,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.95" customHeight="1">
+    <row r="32" spans="1:11" ht="16" customHeight="1">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -2764,7 +2839,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.95" customHeight="1">
+    <row r="33" spans="1:11" ht="16" customHeight="1">
       <c r="A33" s="7">
         <v>28</v>
       </c>
@@ -2799,7 +2874,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.95" customHeight="1">
+    <row r="34" spans="1:11" ht="16" customHeight="1">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2834,7 +2909,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15.95" customHeight="1">
+    <row r="35" spans="1:11" ht="16" customHeight="1">
       <c r="A35" s="3">
         <v>30</v>
       </c>
@@ -2869,7 +2944,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.95" customHeight="1">
+    <row r="36" spans="1:11" ht="16" customHeight="1">
       <c r="A36" s="3">
         <v>100</v>
       </c>
@@ -2904,12 +2979,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.95" customHeight="1">
+    <row r="37" spans="1:11" ht="16" customHeight="1">
       <c r="A37" s="5">
         <v>9</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>185</v>
+        <v>394</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>78</v>
@@ -2918,10 +2993,10 @@
         <v>9599000</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>26</v>
@@ -2930,21 +3005,21 @@
         <v>58</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J37" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="K37" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="38" spans="1:11" ht="16" customHeight="1">
       <c r="A38" s="5">
         <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>78</v>
@@ -2953,10 +3028,10 @@
         <v>9599000</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>41</v>
@@ -2965,21 +3040,21 @@
         <v>27</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J38" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="39" spans="1:11" ht="16" customHeight="1">
       <c r="A39" s="7">
         <v>32</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>108</v>
@@ -2988,7 +3063,7 @@
         <v>9205000</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>143</v>
@@ -3000,21 +3075,21 @@
         <v>58</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J39" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="K39" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="40" spans="1:11" ht="16" customHeight="1">
       <c r="A40" s="7">
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>108</v>
@@ -3023,10 +3098,10 @@
         <v>9159000</v>
       </c>
       <c r="E40" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>200</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>41</v>
@@ -3035,21 +3110,21 @@
         <v>58</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J40" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K40" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="K40" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="41" spans="1:11" ht="16" customHeight="1">
       <c r="A41" s="7">
         <v>34</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>108</v>
@@ -3058,7 +3133,7 @@
         <v>9119000</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>100</v>
@@ -3070,21 +3145,21 @@
         <v>58</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15.95" customHeight="1">
+    <row r="42" spans="1:11" ht="16" customHeight="1">
       <c r="A42" s="3">
         <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -3093,10 +3168,10 @@
         <v>9312000</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>115</v>
@@ -3105,21 +3180,21 @@
         <v>27</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="43" spans="1:11" ht="16" customHeight="1">
       <c r="A43" s="7">
         <v>110</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>108</v>
@@ -3140,21 +3215,21 @@
         <v>58</v>
       </c>
       <c r="I43" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="K43" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="K43" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="44" spans="1:11" ht="16" customHeight="1">
       <c r="A44" s="7">
         <v>120</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>108</v>
@@ -3163,33 +3238,33 @@
         <v>10463000</v>
       </c>
       <c r="E44" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="I44" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="J44" s="7" t="s">
+      <c r="K44" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="K44" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="45" spans="1:11" ht="16" customHeight="1">
       <c r="A45" s="7">
         <v>130</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>108</v>
@@ -3198,10 +3273,10 @@
         <v>10224000</v>
       </c>
       <c r="E45" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>26</v>
@@ -3210,21 +3285,21 @@
         <v>58</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J45" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="K45" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K45" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="46" spans="1:11" ht="16" customHeight="1">
       <c r="A46" s="7">
         <v>140</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>108</v>
@@ -3233,10 +3308,10 @@
         <v>10284000</v>
       </c>
       <c r="E46" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>41</v>
@@ -3245,21 +3320,21 @@
         <v>58</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J46" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K46" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="K46" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="47" spans="1:11" ht="16" customHeight="1">
       <c r="A47" s="5">
         <v>150</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>78</v>
@@ -3268,7 +3343,7 @@
         <v>10224000</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>73</v>
@@ -3280,21 +3355,21 @@
         <v>58</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J47" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="K47" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="K47" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="48" spans="1:11" ht="16" customHeight="1">
       <c r="A48" s="5">
         <v>160</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>78</v>
@@ -3303,10 +3378,10 @@
         <v>10128000</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>115</v>
@@ -3315,21 +3390,21 @@
         <v>58</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J48" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="K48" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="K48" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="49" spans="1:11" ht="16" customHeight="1">
       <c r="A49" s="3">
         <v>170</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>23</v>
@@ -3338,10 +3413,10 @@
         <v>10464000</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>26</v>
@@ -3350,21 +3425,21 @@
         <v>27</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="50" spans="1:11" ht="16" customHeight="1">
       <c r="A50" s="3">
         <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>244</v>
+        <v>393</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -3373,10 +3448,10 @@
         <v>10224000</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>26</v>
@@ -3385,21 +3460,21 @@
         <v>58</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="15.95" customHeight="1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="16" customHeight="1">
       <c r="A51" s="7">
         <v>190</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>108</v>
@@ -3408,10 +3483,10 @@
         <v>11138000</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>26</v>
@@ -3420,21 +3495,21 @@
         <v>58</v>
       </c>
       <c r="I51" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="J51" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="15.95" customHeight="1">
+    </row>
+    <row r="52" spans="1:11" ht="16" customHeight="1">
       <c r="A52" s="7">
         <v>200</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>108</v>
@@ -3443,7 +3518,7 @@
         <v>11553000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>143</v>
@@ -3455,21 +3530,21 @@
         <v>58</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.95" customHeight="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="16" customHeight="1">
       <c r="A53" s="7">
         <v>201</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>108</v>
@@ -3478,10 +3553,10 @@
         <v>10880000</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>26</v>
@@ -3490,21 +3565,21 @@
         <v>58</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.95" customHeight="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="16" customHeight="1">
       <c r="A54" s="7">
         <v>202</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>263</v>
+        <v>385</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>108</v>
@@ -3513,10 +3588,10 @@
         <v>11399000</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
@@ -3525,21 +3600,21 @@
         <v>58</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="15.95" customHeight="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="16" customHeight="1">
       <c r="A55" s="7">
         <v>203</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>268</v>
+        <v>386</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>108</v>
@@ -3548,10 +3623,10 @@
         <v>12042000</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>26</v>
@@ -3560,21 +3635,21 @@
         <v>58</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.95" customHeight="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="16" customHeight="1">
       <c r="A56" s="3">
         <v>204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -3583,10 +3658,10 @@
         <v>11564000</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>26</v>
@@ -3595,21 +3670,21 @@
         <v>27</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="15.95" customHeight="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="16" customHeight="1">
       <c r="A57" s="3">
         <v>205</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>278</v>
+        <v>387</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>23</v>
@@ -3618,10 +3693,10 @@
         <v>11956000</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>26</v>
@@ -3630,13 +3705,13 @@
         <v>58</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3644,7 +3719,7 @@
         <v>206</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>108</v>
@@ -3653,10 +3728,10 @@
         <v>12369000</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>26</v>
@@ -3665,13 +3740,13 @@
         <v>58</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3679,7 +3754,7 @@
         <v>207</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>108</v>
@@ -3688,10 +3763,10 @@
         <v>12316000</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>26</v>
@@ -3700,13 +3775,13 @@
         <v>58</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3714,7 +3789,7 @@
         <v>208</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>108</v>
@@ -3723,7 +3798,7 @@
         <v>11763000</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>153</v>
@@ -3735,13 +3810,13 @@
         <v>58</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3749,7 +3824,7 @@
         <v>209</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>295</v>
+        <v>389</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>23</v>
@@ -3758,10 +3833,10 @@
         <v>12054000</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>26</v>
@@ -3770,13 +3845,13 @@
         <v>58</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3784,7 +3859,7 @@
         <v>210</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>23</v>
@@ -3793,7 +3868,7 @@
         <v>2850000</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>32</v>
@@ -3805,13 +3880,13 @@
         <v>27</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3819,7 +3894,7 @@
         <v>211</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>23</v>
@@ -3828,7 +3903,7 @@
         <v>2900000</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>85</v>
@@ -3837,16 +3912,16 @@
         <v>41</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3854,7 +3929,7 @@
         <v>212</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>23</v>
@@ -3863,7 +3938,7 @@
         <v>2700000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>32</v>
@@ -3875,13 +3950,13 @@
         <v>27</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3889,7 +3964,7 @@
         <v>213</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -3898,7 +3973,7 @@
         <v>1911000</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>32</v>
@@ -3910,13 +3985,13 @@
         <v>27</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3924,7 +3999,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -3933,25 +4008,25 @@
         <v>1860000</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3959,7 +4034,7 @@
         <v>215</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -3968,7 +4043,7 @@
         <v>1875000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>32</v>
@@ -3977,16 +4052,16 @@
         <v>41</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3994,7 +4069,7 @@
         <v>216</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>108</v>
@@ -4003,25 +4078,25 @@
         <v>13014000</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -4029,7 +4104,7 @@
         <v>217</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>108</v>
@@ -4038,10 +4113,10 @@
         <v>12926000</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>26</v>
@@ -4050,13 +4125,13 @@
         <v>58</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4064,7 +4139,7 @@
         <v>218</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>108</v>
@@ -4073,25 +4148,25 @@
         <v>13994000</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4099,7 +4174,7 @@
         <v>219</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>337</v>
+        <v>391</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>108</v>
@@ -4108,10 +4183,10 @@
         <v>13994000</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>26</v>
@@ -4120,13 +4195,13 @@
         <v>58</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4134,7 +4209,7 @@
         <v>220</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>108</v>
@@ -4143,10 +4218,10 @@
         <v>14149000</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>26</v>
@@ -4155,13 +4230,13 @@
         <v>58</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4169,7 +4244,7 @@
         <v>221</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>108</v>
@@ -4178,10 +4253,10 @@
         <v>14494000</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>26</v>
@@ -4190,13 +4265,13 @@
         <v>58</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4204,7 +4279,7 @@
         <v>222</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>108</v>
@@ -4213,25 +4288,25 @@
         <v>14446000</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4239,7 +4314,7 @@
         <v>223</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>108</v>
@@ -4248,10 +4323,10 @@
         <v>14274000</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>26</v>
@@ -4260,13 +4335,13 @@
         <v>58</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4274,7 +4349,7 @@
         <v>224</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>23</v>
@@ -4283,7 +4358,7 @@
         <v>3634000</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>32</v>
@@ -4295,13 +4370,13 @@
         <v>58</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -4309,7 +4384,7 @@
         <v>225</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>23</v>
@@ -4330,13 +4405,13 @@
         <v>58</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4344,7 +4419,7 @@
         <v>226</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>23</v>
@@ -4353,7 +4428,7 @@
         <v>3634000</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>32</v>
@@ -4365,79 +4440,189 @@
         <v>58</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J78" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="3">
+        <v>227</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="3">
+        <v>5712000</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="F79" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="3">
+        <v>228</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" s="3">
+        <v>6672000</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
+      <c r="A81" s="3">
+        <v>229</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="3">
+        <v>7152000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
+      <c r="A82" s="3">
+        <v>230</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="3">
+        <v>8448000</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
+      <c r="A83" s="3">
+        <v>231</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" s="3">
+        <v>9552000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="3"/>
@@ -4691,8 +4876,10 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I76:I78" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/" xr:uid="{7A9DFC0A-9F74-45F0-B51F-2573F164C957}"/>
+    <hyperlink ref="I79:I82" r:id="rId2" display="https://www.tiktok.com/@pantautech.id/" xr:uid="{96E1CE99-BAFC-42EA-8AC1-D7E8025E9F6B}"/>
+    <hyperlink ref="I83" r:id="rId3" xr:uid="{28087103-1C22-43A6-8B5B-11D66B579C81}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6710B9B8-7790-4689-B288-AF8BB31FFC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E722A8A-FD0C-4E75-9AEA-EC2FEC3B33F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>https://www.tiktok.com/@pantautech.id/photo/7647551966968646919?is_from_webapp=1&amp;sender_device=pc</t>
   </si>
   <si>
-    <t>https://s.shopee.co.id/4qDCekqJ86</t>
-  </si>
-  <si>
     <t>ThinkPad T14 G1.webp</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>ThinkPad P51.webp</t>
   </si>
   <si>
-    <t>ThinkPad P52 (TEKNIK)</t>
-  </si>
-  <si>
     <t>Intel Core i7-8565H</t>
   </si>
   <si>
@@ -1224,6 +1218,12 @@
   </si>
   <si>
     <t>Advan Pixwar</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/8pjwtwM63b</t>
+  </si>
+  <si>
+    <t>(HABIS)ThinkPad P52 TEKNIK</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1707,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="37.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
@@ -1940,7 +1940,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="3">
-        <v>4454000</v>
+        <v>4655000</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>46</v>
@@ -1958,10 +1958,10 @@
         <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16" customHeight="1">
@@ -1969,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>23</v>
@@ -1978,10 +1978,10 @@
         <v>4235000</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>26</v>
@@ -1993,10 +1993,10 @@
         <v>48</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16" customHeight="1">
@@ -2004,7 +2004,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>23</v>
@@ -2013,25 +2013,25 @@
         <v>5509000</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16" customHeight="1">
@@ -2039,7 +2039,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
@@ -2048,10 +2048,10 @@
         <v>4883000</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>41</v>
@@ -2063,10 +2063,10 @@
         <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="16" customHeight="1">
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
@@ -2083,25 +2083,25 @@
         <v>5424000</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16" customHeight="1">
@@ -2109,7 +2109,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>23</v>
@@ -2118,25 +2118,25 @@
         <v>5664000</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16" customHeight="1">
@@ -2144,19 +2144,19 @@
         <v>90</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="5">
         <v>5951000</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>41</v>
@@ -2165,13 +2165,13 @@
         <v>27</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="16" customHeight="1">
@@ -2179,19 +2179,19 @@
         <v>91</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" s="5">
         <v>5759000</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>41</v>
@@ -2200,13 +2200,13 @@
         <v>27</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="16" customHeight="1">
@@ -2214,19 +2214,19 @@
         <v>92</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" s="5">
         <v>5466000</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>41</v>
@@ -2235,13 +2235,13 @@
         <v>27</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16" customHeight="1">
@@ -2249,19 +2249,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5">
         <v>6788000</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>41</v>
@@ -2270,13 +2270,13 @@
         <v>27</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="16" customHeight="1">
@@ -2284,34 +2284,34 @@
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D17" s="5">
         <v>6620000</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="16" customHeight="1">
@@ -2319,19 +2319,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D18" s="5">
         <v>6881000</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>41</v>
@@ -2340,13 +2340,13 @@
         <v>27</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="16" customHeight="1">
@@ -2354,19 +2354,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" s="7">
         <v>6416000</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>41</v>
@@ -2375,13 +2375,13 @@
         <v>27</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16" customHeight="1">
@@ -2389,7 +2389,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>23</v>
@@ -2398,25 +2398,25 @@
         <v>6958000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16" customHeight="1">
@@ -2424,7 +2424,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
@@ -2433,10 +2433,10 @@
         <v>6240000</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -2445,13 +2445,13 @@
         <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>23</v>
@@ -2468,10 +2468,10 @@
         <v>6912000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>26</v>
@@ -2480,13 +2480,13 @@
         <v>27</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="16" customHeight="1">
@@ -2494,7 +2494,7 @@
         <v>83</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>23</v>
@@ -2503,10 +2503,10 @@
         <v>6993000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>26</v>
@@ -2518,10 +2518,10 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="16" customHeight="1">
@@ -2529,19 +2529,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24" s="5">
         <v>7391000</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>41</v>
@@ -2550,13 +2550,13 @@
         <v>27</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="16" customHeight="1">
@@ -2564,34 +2564,34 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" s="5">
         <v>7434000</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="16" customHeight="1">
@@ -2599,19 +2599,19 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D26" s="5">
         <v>7583000</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>41</v>
@@ -2620,13 +2620,13 @@
         <v>27</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="16" customHeight="1">
@@ -2634,19 +2634,19 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D27" s="7">
         <v>7949000</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>41</v>
@@ -2655,13 +2655,13 @@
         <v>27</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="16" customHeight="1">
@@ -2669,7 +2669,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
@@ -2678,25 +2678,25 @@
         <v>7500000</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="16" customHeight="1">
@@ -2704,19 +2704,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D29" s="5">
         <v>7871000</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>41</v>
@@ -2725,13 +2725,13 @@
         <v>27</v>
       </c>
       <c r="I29" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="16" customHeight="1">
@@ -2739,19 +2739,19 @@
         <v>8</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D30" s="5">
         <v>8207000</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>41</v>
@@ -2760,13 +2760,13 @@
         <v>27</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="16" customHeight="1">
@@ -2774,34 +2774,34 @@
         <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D31" s="7">
         <v>8201000</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="16" customHeight="1">
@@ -2809,34 +2809,34 @@
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D32" s="5">
         <v>8364000</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16" customHeight="1">
@@ -2844,34 +2844,34 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D33" s="7">
         <v>8062000</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16" customHeight="1">
@@ -2879,34 +2879,34 @@
         <v>29</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D34" s="7">
         <v>8099000</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="16" customHeight="1">
@@ -2914,7 +2914,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
@@ -2923,10 +2923,10 @@
         <v>8544000</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>26</v>
@@ -2935,13 +2935,13 @@
         <v>27</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="16" customHeight="1">
@@ -2949,7 +2949,7 @@
         <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>23</v>
@@ -2958,10 +2958,10 @@
         <v>8544000</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>26</v>
@@ -2970,13 +2970,13 @@
         <v>27</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="16" customHeight="1">
@@ -2984,34 +2984,34 @@
         <v>9</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D37" s="5">
         <v>9599000</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K37" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="16" customHeight="1">
@@ -3019,19 +3019,19 @@
         <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D38" s="5">
         <v>9599000</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>41</v>
@@ -3040,13 +3040,13 @@
         <v>27</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="16" customHeight="1">
@@ -3054,34 +3054,34 @@
         <v>32</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D39" s="7">
         <v>9205000</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="16" customHeight="1">
@@ -3089,34 +3089,34 @@
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D40" s="7">
         <v>9159000</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="16" customHeight="1">
@@ -3124,34 +3124,34 @@
         <v>34</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D41" s="7">
         <v>9119000</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16" customHeight="1">
@@ -3159,7 +3159,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -3168,25 +3168,25 @@
         <v>9312000</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="16" customHeight="1">
@@ -3194,34 +3194,34 @@
         <v>110</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D43" s="7">
         <v>10182000</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I43" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="7" t="s">
         <v>212</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="16" customHeight="1">
@@ -3229,34 +3229,34 @@
         <v>120</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D44" s="7">
         <v>10463000</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K44" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="16" customHeight="1">
@@ -3264,34 +3264,34 @@
         <v>130</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D45" s="7">
         <v>10224000</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="16" customHeight="1">
@@ -3299,34 +3299,34 @@
         <v>140</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D46" s="7">
         <v>10284000</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="16" customHeight="1">
@@ -3334,34 +3334,34 @@
         <v>150</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D47" s="5">
         <v>10224000</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="16" customHeight="1">
@@ -3369,34 +3369,34 @@
         <v>160</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D48" s="5">
         <v>10128000</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="16" customHeight="1">
@@ -3404,7 +3404,7 @@
         <v>170</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>23</v>
@@ -3413,10 +3413,10 @@
         <v>10464000</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>26</v>
@@ -3425,13 +3425,13 @@
         <v>27</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="16" customHeight="1">
@@ -3439,7 +3439,7 @@
         <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -3448,25 +3448,25 @@
         <v>10224000</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16" customHeight="1">
@@ -3474,34 +3474,34 @@
         <v>190</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D51" s="7">
         <v>11138000</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I51" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16" customHeight="1">
@@ -3509,34 +3509,34 @@
         <v>200</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D52" s="7">
         <v>11553000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="16" customHeight="1">
@@ -3544,34 +3544,34 @@
         <v>201</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D53" s="7">
         <v>10880000</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16" customHeight="1">
@@ -3579,34 +3579,34 @@
         <v>202</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D54" s="7">
         <v>11399000</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16" customHeight="1">
@@ -3614,34 +3614,34 @@
         <v>203</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D55" s="7">
         <v>12042000</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16" customHeight="1">
@@ -3649,7 +3649,7 @@
         <v>204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -3658,10 +3658,10 @@
         <v>11564000</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>26</v>
@@ -3670,13 +3670,13 @@
         <v>27</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16" customHeight="1">
@@ -3684,7 +3684,7 @@
         <v>205</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>23</v>
@@ -3693,25 +3693,25 @@
         <v>11956000</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3719,34 +3719,34 @@
         <v>206</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D58" s="3">
         <v>12369000</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I58" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3754,34 +3754,34 @@
         <v>207</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D59" s="3">
         <v>12316000</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3789,34 +3789,34 @@
         <v>208</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D60" s="3">
         <v>11763000</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3824,7 +3824,7 @@
         <v>209</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>23</v>
@@ -3833,25 +3833,25 @@
         <v>12054000</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3859,7 +3859,7 @@
         <v>210</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>23</v>
@@ -3868,7 +3868,7 @@
         <v>2850000</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>32</v>
@@ -3880,13 +3880,13 @@
         <v>27</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3894,7 +3894,7 @@
         <v>211</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>23</v>
@@ -3903,25 +3903,25 @@
         <v>2900000</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3929,7 +3929,7 @@
         <v>212</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>23</v>
@@ -3938,7 +3938,7 @@
         <v>2700000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>32</v>
@@ -3950,13 +3950,13 @@
         <v>27</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3964,7 +3964,7 @@
         <v>213</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -3973,7 +3973,7 @@
         <v>1911000</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>32</v>
@@ -3985,13 +3985,13 @@
         <v>27</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3999,7 +3999,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -4008,25 +4008,25 @@
         <v>1860000</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4034,7 +4034,7 @@
         <v>215</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -4043,7 +4043,7 @@
         <v>1875000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>32</v>
@@ -4052,16 +4052,16 @@
         <v>41</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -4069,34 +4069,34 @@
         <v>216</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D68" s="3">
         <v>13014000</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -4104,34 +4104,34 @@
         <v>217</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D69" s="3">
         <v>12926000</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4139,34 +4139,34 @@
         <v>218</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D70" s="3">
         <v>13994000</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4174,34 +4174,34 @@
         <v>219</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D71" s="3">
         <v>13994000</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4209,34 +4209,34 @@
         <v>220</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D72" s="3">
         <v>14149000</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4244,34 +4244,34 @@
         <v>221</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D73" s="3">
         <v>14494000</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4279,34 +4279,34 @@
         <v>222</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D74" s="3">
         <v>14446000</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4314,34 +4314,34 @@
         <v>223</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D75" s="3">
         <v>14274000</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4349,7 +4349,7 @@
         <v>224</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>23</v>
@@ -4358,7 +4358,7 @@
         <v>3634000</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>32</v>
@@ -4367,16 +4367,16 @@
         <v>26</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -4384,7 +4384,7 @@
         <v>225</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>23</v>
@@ -4393,25 +4393,25 @@
         <v>5520000</v>
       </c>
       <c r="E77" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4419,7 +4419,7 @@
         <v>226</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>23</v>
@@ -4428,7 +4428,7 @@
         <v>3634000</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>32</v>
@@ -4437,16 +4437,16 @@
         <v>26</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -4454,7 +4454,7 @@
         <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>23</v>
@@ -4463,25 +4463,25 @@
         <v>5712000</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -4489,7 +4489,7 @@
         <v>228</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>23</v>
@@ -4498,25 +4498,25 @@
         <v>6672000</v>
       </c>
       <c r="E80" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -4524,7 +4524,7 @@
         <v>229</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>23</v>
@@ -4533,25 +4533,25 @@
         <v>7152000</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4559,7 +4559,7 @@
         <v>230</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>23</v>
@@ -4568,25 +4568,25 @@
         <v>8448000</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4594,7 +4594,7 @@
         <v>231</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>23</v>
@@ -4603,25 +4603,25 @@
         <v>9552000</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="84" spans="1:11">

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E722A8A-FD0C-4E75-9AEA-EC2FEC3B33F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C744F72E-068C-4DA0-A462-F91B32347B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -215,9 +215,6 @@
     <t>512GB</t>
   </si>
   <si>
-    <t>https://s.shopee.co.id/20t1Hq2YNT</t>
-  </si>
-  <si>
     <t>HP Elitebook 845 G8.webp</t>
   </si>
   <si>
@@ -1112,9 +1109,6 @@
     <t>Dell Latitude 5400 (TERLARIS)</t>
   </si>
   <si>
-    <t>HP Elitebook 845 G8 (TERLARIS)</t>
-  </si>
-  <si>
     <t>Asus TUF FX504GE (GAMING)</t>
   </si>
   <si>
@@ -1224,6 +1218,12 @@
   </si>
   <si>
     <t>(HABIS)ThinkPad P52 TEKNIK</t>
+  </si>
+  <si>
+    <t>(HARGA NAIK) HP Elitebook 845 G8 (TERLARIS)</t>
+  </si>
+  <si>
+    <t>https://s.shopee.co.id/2g9b9rX8re</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1958,7 @@
         <v>48</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>49</v>
@@ -2004,13 +2004,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>5509000</v>
+        <v>5700000</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>55</v>
@@ -2028,10 +2028,10 @@
         <v>48</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16" customHeight="1">
@@ -2039,7 +2039,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
@@ -2048,10 +2048,10 @@
         <v>4883000</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>41</v>
@@ -2063,10 +2063,10 @@
         <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="16" customHeight="1">
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
@@ -2083,10 +2083,10 @@
         <v>5424000</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
@@ -2098,10 +2098,10 @@
         <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16" customHeight="1">
@@ -2109,7 +2109,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>23</v>
@@ -2118,10 +2118,10 @@
         <v>5664000</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>26</v>
@@ -2130,13 +2130,13 @@
         <v>57</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16" customHeight="1">
@@ -2144,19 +2144,19 @@
         <v>90</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="D13" s="5">
         <v>5951000</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>41</v>
@@ -2165,13 +2165,13 @@
         <v>27</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="16" customHeight="1">
@@ -2179,19 +2179,19 @@
         <v>91</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="5">
         <v>5759000</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>41</v>
@@ -2200,13 +2200,13 @@
         <v>27</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="16" customHeight="1">
@@ -2214,19 +2214,19 @@
         <v>92</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="5">
         <v>5466000</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>41</v>
@@ -2235,13 +2235,13 @@
         <v>27</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16" customHeight="1">
@@ -2249,16 +2249,16 @@
         <v>6</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="5">
         <v>6788000</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>56</v>
@@ -2270,13 +2270,13 @@
         <v>27</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="16" customHeight="1">
@@ -2284,19 +2284,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="5">
         <v>6620000</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>41</v>
@@ -2305,13 +2305,13 @@
         <v>57</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="16" customHeight="1">
@@ -2319,16 +2319,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="5">
         <v>6881000</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>56</v>
@@ -2340,13 +2340,13 @@
         <v>27</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="16" customHeight="1">
@@ -2354,19 +2354,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>105</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>106</v>
       </c>
       <c r="D19" s="7">
         <v>6416000</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>41</v>
@@ -2375,13 +2375,13 @@
         <v>27</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16" customHeight="1">
@@ -2389,7 +2389,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>23</v>
@@ -2398,25 +2398,25 @@
         <v>6958000</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="16" customHeight="1">
@@ -2424,7 +2424,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
@@ -2433,10 +2433,10 @@
         <v>6240000</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -2445,13 +2445,13 @@
         <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="16" customHeight="1">
@@ -2459,7 +2459,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>23</v>
@@ -2468,10 +2468,10 @@
         <v>6912000</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>26</v>
@@ -2480,13 +2480,13 @@
         <v>27</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="16" customHeight="1">
@@ -2494,7 +2494,7 @@
         <v>83</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>23</v>
@@ -2503,10 +2503,10 @@
         <v>6993000</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>26</v>
@@ -2518,10 +2518,10 @@
         <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="16" customHeight="1">
@@ -2529,19 +2529,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D24" s="5">
         <v>7391000</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>41</v>
@@ -2550,13 +2550,13 @@
         <v>27</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="K24" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="16" customHeight="1">
@@ -2564,19 +2564,19 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" s="5">
         <v>7434000</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>41</v>
@@ -2585,13 +2585,13 @@
         <v>57</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J25" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="16" customHeight="1">
@@ -2599,19 +2599,19 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5">
         <v>7583000</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>41</v>
@@ -2620,13 +2620,13 @@
         <v>27</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J26" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="16" customHeight="1">
@@ -2634,19 +2634,19 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="7">
         <v>7949000</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>41</v>
@@ -2655,13 +2655,13 @@
         <v>27</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J27" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="16" customHeight="1">
@@ -2669,7 +2669,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
@@ -2678,25 +2678,25 @@
         <v>7500000</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="16" customHeight="1">
@@ -2704,19 +2704,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="5">
         <v>7871000</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>41</v>
@@ -2725,13 +2725,13 @@
         <v>27</v>
       </c>
       <c r="I29" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="16" customHeight="1">
@@ -2739,19 +2739,19 @@
         <v>8</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="5">
         <v>8207000</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>41</v>
@@ -2760,13 +2760,13 @@
         <v>27</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J30" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="16" customHeight="1">
@@ -2774,16 +2774,16 @@
         <v>23</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="7">
         <v>8201000</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>56</v>
@@ -2795,13 +2795,13 @@
         <v>57</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J31" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="16" customHeight="1">
@@ -2809,19 +2809,19 @@
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="5">
         <v>8364000</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>41</v>
@@ -2830,13 +2830,13 @@
         <v>57</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="16" customHeight="1">
@@ -2844,19 +2844,19 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="7">
         <v>8062000</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>41</v>
@@ -2865,13 +2865,13 @@
         <v>57</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J33" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="K33" s="7" t="s">
         <v>168</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="16" customHeight="1">
@@ -2879,19 +2879,19 @@
         <v>29</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" s="7">
         <v>8099000</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>41</v>
@@ -2900,13 +2900,13 @@
         <v>57</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J34" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K34" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="16" customHeight="1">
@@ -2914,7 +2914,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
@@ -2923,10 +2923,10 @@
         <v>8544000</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>26</v>
@@ -2935,13 +2935,13 @@
         <v>27</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="16" customHeight="1">
@@ -2949,7 +2949,7 @@
         <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>23</v>
@@ -2958,10 +2958,10 @@
         <v>8544000</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>26</v>
@@ -2970,13 +2970,13 @@
         <v>27</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="K36" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="16" customHeight="1">
@@ -2984,19 +2984,19 @@
         <v>9</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D37" s="5">
         <v>9599000</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>26</v>
@@ -3005,13 +3005,13 @@
         <v>57</v>
       </c>
       <c r="I37" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="K37" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="16" customHeight="1">
@@ -3019,19 +3019,19 @@
         <v>31</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D38" s="5">
         <v>9599000</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>41</v>
@@ -3040,13 +3040,13 @@
         <v>27</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J38" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="16" customHeight="1">
@@ -3054,19 +3054,19 @@
         <v>32</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" s="7">
         <v>9205000</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>41</v>
@@ -3075,13 +3075,13 @@
         <v>57</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J39" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="16" customHeight="1">
@@ -3089,19 +3089,19 @@
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D40" s="7">
         <v>9159000</v>
       </c>
       <c r="E40" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>41</v>
@@ -3110,13 +3110,13 @@
         <v>57</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J40" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="K40" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="16" customHeight="1">
@@ -3124,19 +3124,19 @@
         <v>34</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D41" s="7">
         <v>9119000</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>41</v>
@@ -3145,13 +3145,13 @@
         <v>57</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="16" customHeight="1">
@@ -3159,7 +3159,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
@@ -3168,25 +3168,25 @@
         <v>9312000</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>27</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="16" customHeight="1">
@@ -3194,19 +3194,19 @@
         <v>110</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" s="7">
         <v>10182000</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>26</v>
@@ -3215,13 +3215,13 @@
         <v>57</v>
       </c>
       <c r="I43" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="K43" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="16" customHeight="1">
@@ -3229,34 +3229,34 @@
         <v>120</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="7">
         <v>10463000</v>
       </c>
       <c r="E44" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>214</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>215</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="J44" s="7" t="s">
+      <c r="K44" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="16" customHeight="1">
@@ -3264,19 +3264,19 @@
         <v>130</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D45" s="7">
         <v>10224000</v>
       </c>
       <c r="E45" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>26</v>
@@ -3285,13 +3285,13 @@
         <v>57</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J45" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="K45" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="16" customHeight="1">
@@ -3299,19 +3299,19 @@
         <v>140</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="7">
         <v>10284000</v>
       </c>
       <c r="E46" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>41</v>
@@ -3320,13 +3320,13 @@
         <v>57</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J46" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K46" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="16" customHeight="1">
@@ -3334,19 +3334,19 @@
         <v>150</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="5">
         <v>10224000</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>26</v>
@@ -3355,13 +3355,13 @@
         <v>57</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J47" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="K47" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="16" customHeight="1">
@@ -3369,34 +3369,34 @@
         <v>160</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" s="5">
         <v>10128000</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>184</v>
-      </c>
       <c r="G48" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>57</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J48" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="K48" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="K48" s="5" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="16" customHeight="1">
@@ -3404,7 +3404,7 @@
         <v>170</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>23</v>
@@ -3413,10 +3413,10 @@
         <v>10464000</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>26</v>
@@ -3425,13 +3425,13 @@
         <v>27</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="16" customHeight="1">
@@ -3439,7 +3439,7 @@
         <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -3448,10 +3448,10 @@
         <v>10224000</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>26</v>
@@ -3460,13 +3460,13 @@
         <v>57</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16" customHeight="1">
@@ -3474,19 +3474,19 @@
         <v>190</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D51" s="7">
         <v>11138000</v>
       </c>
       <c r="E51" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F51" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>26</v>
@@ -3495,13 +3495,13 @@
         <v>57</v>
       </c>
       <c r="I51" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="K51" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16" customHeight="1">
@@ -3509,19 +3509,19 @@
         <v>200</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D52" s="7">
         <v>11553000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>26</v>
@@ -3530,13 +3530,13 @@
         <v>57</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J52" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="K52" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="16" customHeight="1">
@@ -3544,19 +3544,19 @@
         <v>201</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D53" s="7">
         <v>10880000</v>
       </c>
       <c r="E53" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>26</v>
@@ -3565,13 +3565,13 @@
         <v>57</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J53" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="K53" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="K53" s="7" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16" customHeight="1">
@@ -3579,19 +3579,19 @@
         <v>202</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D54" s="7">
         <v>11399000</v>
       </c>
       <c r="E54" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
@@ -3600,13 +3600,13 @@
         <v>57</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J54" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16" customHeight="1">
@@ -3614,19 +3614,19 @@
         <v>203</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D55" s="7">
         <v>12042000</v>
       </c>
       <c r="E55" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>26</v>
@@ -3635,13 +3635,13 @@
         <v>57</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J55" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="K55" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16" customHeight="1">
@@ -3649,7 +3649,7 @@
         <v>204</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -3658,10 +3658,10 @@
         <v>11564000</v>
       </c>
       <c r="E56" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>26</v>
@@ -3670,13 +3670,13 @@
         <v>27</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J56" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16" customHeight="1">
@@ -3684,7 +3684,7 @@
         <v>205</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>23</v>
@@ -3693,10 +3693,10 @@
         <v>11956000</v>
       </c>
       <c r="E57" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>26</v>
@@ -3705,13 +3705,13 @@
         <v>57</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J57" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3719,19 +3719,19 @@
         <v>206</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" s="3">
         <v>12369000</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>26</v>
@@ -3740,13 +3740,13 @@
         <v>57</v>
       </c>
       <c r="I58" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3754,19 +3754,19 @@
         <v>207</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" s="3">
         <v>12316000</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>26</v>
@@ -3775,13 +3775,13 @@
         <v>57</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J59" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3789,19 +3789,19 @@
         <v>208</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" s="3">
         <v>11763000</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>26</v>
@@ -3810,13 +3810,13 @@
         <v>57</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J60" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3824,7 +3824,7 @@
         <v>209</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>23</v>
@@ -3833,10 +3833,10 @@
         <v>12054000</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>26</v>
@@ -3845,13 +3845,13 @@
         <v>57</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J61" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3859,7 +3859,7 @@
         <v>210</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>23</v>
@@ -3868,7 +3868,7 @@
         <v>2850000</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>32</v>
@@ -3880,13 +3880,13 @@
         <v>27</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J62" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3894,7 +3894,7 @@
         <v>211</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>23</v>
@@ -3903,25 +3903,25 @@
         <v>2900000</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="J63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3929,7 +3929,7 @@
         <v>212</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>23</v>
@@ -3938,7 +3938,7 @@
         <v>2700000</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>32</v>
@@ -3950,13 +3950,13 @@
         <v>27</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J64" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3964,7 +3964,7 @@
         <v>213</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -3973,7 +3973,7 @@
         <v>1911000</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>32</v>
@@ -3985,13 +3985,13 @@
         <v>27</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3999,7 +3999,7 @@
         <v>214</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -4008,25 +4008,25 @@
         <v>1860000</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -4034,7 +4034,7 @@
         <v>215</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -4043,7 +4043,7 @@
         <v>1875000</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>32</v>
@@ -4052,16 +4052,16 @@
         <v>41</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -4069,34 +4069,34 @@
         <v>216</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D68" s="3">
         <v>13014000</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J68" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -4104,19 +4104,19 @@
         <v>217</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" s="3">
         <v>12926000</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>26</v>
@@ -4125,13 +4125,13 @@
         <v>57</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -4139,34 +4139,34 @@
         <v>218</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" s="3">
         <v>13994000</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -4174,19 +4174,19 @@
         <v>219</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D71" s="3">
         <v>13994000</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>26</v>
@@ -4195,13 +4195,13 @@
         <v>57</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4209,19 +4209,19 @@
         <v>220</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" s="3">
         <v>14149000</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>26</v>
@@ -4230,13 +4230,13 @@
         <v>57</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -4244,19 +4244,19 @@
         <v>221</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D73" s="3">
         <v>14494000</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>26</v>
@@ -4265,13 +4265,13 @@
         <v>57</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -4279,34 +4279,34 @@
         <v>222</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D74" s="3">
         <v>14446000</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -4314,19 +4314,19 @@
         <v>223</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D75" s="3">
         <v>14274000</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>26</v>
@@ -4335,13 +4335,13 @@
         <v>57</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -4349,7 +4349,7 @@
         <v>224</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>23</v>
@@ -4358,7 +4358,7 @@
         <v>3634000</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>32</v>
@@ -4370,13 +4370,13 @@
         <v>57</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -4384,7 +4384,7 @@
         <v>225</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>23</v>
@@ -4405,13 +4405,13 @@
         <v>57</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -4419,7 +4419,7 @@
         <v>226</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>23</v>
@@ -4428,7 +4428,7 @@
         <v>3634000</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>32</v>
@@ -4440,13 +4440,13 @@
         <v>57</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -4454,7 +4454,7 @@
         <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>23</v>
@@ -4463,25 +4463,25 @@
         <v>5712000</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -4489,7 +4489,7 @@
         <v>228</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>23</v>
@@ -4498,10 +4498,10 @@
         <v>6672000</v>
       </c>
       <c r="E80" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>26</v>
@@ -4510,13 +4510,13 @@
         <v>57</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -4524,7 +4524,7 @@
         <v>229</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>23</v>
@@ -4533,25 +4533,25 @@
         <v>7152000</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4559,7 +4559,7 @@
         <v>230</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>23</v>
@@ -4568,10 +4568,10 @@
         <v>8448000</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>26</v>
@@ -4580,13 +4580,13 @@
         <v>57</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4594,7 +4594,7 @@
         <v>231</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>23</v>
@@ -4603,10 +4603,10 @@
         <v>9552000</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>26</v>
@@ -4615,13 +4615,13 @@
         <v>57</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:11">

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C744F72E-068C-4DA0-A462-F91B32347B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6117B2-C098-48D4-B59A-8885BA391DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2010,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>5700000</v>
+        <v>5039000</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>55</v>
@@ -2022,7 +2022,7 @@
         <v>26</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>48</v>

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6117B2-C098-48D4-B59A-8885BA391DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180141C2-5BE5-4082-BE4D-18F75E420598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1223,7 +1223,7 @@
     <t>(HARGA NAIK) HP Elitebook 845 G8 (TERLARIS)</t>
   </si>
   <si>
-    <t>https://s.shopee.co.id/2g9b9rX8re</t>
+    <t>https://s.shopee.co.id/6AjTIUmld0</t>
   </si>
 </sst>
 </file>
@@ -2010,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="3">
-        <v>5039000</v>
+        <v>4988000</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>55</v>

--- a/products_data.xlsx
+++ b/products_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riora\Videos\AFFILIATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180141C2-5BE5-4082-BE4D-18F75E420598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42827F2F-04B9-4C87-A573-FF42EF8907F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="396">
   <si>
     <t>id</t>
   </si>
@@ -1224,6 +1224,9 @@
   </si>
   <si>
     <t>https://s.shopee.co.id/6AjTIUmld0</t>
+  </si>
+  <si>
+    <t>HP Elitebook 845 G7</t>
   </si>
 </sst>
 </file>
@@ -4625,17 +4628,39 @@
       </c>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
+      <c r="A84" s="3">
+        <v>232</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="3">
+        <v>4679000</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="3"/>
@@ -4878,8 +4903,9 @@
     <hyperlink ref="I76:I78" r:id="rId1" display="https://www.tiktok.com/@pantautech.id/" xr:uid="{7A9DFC0A-9F74-45F0-B51F-2573F164C957}"/>
     <hyperlink ref="I79:I82" r:id="rId2" display="https://www.tiktok.com/@pantautech.id/" xr:uid="{96E1CE99-BAFC-42EA-8AC1-D7E8025E9F6B}"/>
     <hyperlink ref="I83" r:id="rId3" xr:uid="{28087103-1C22-43A6-8B5B-11D66B579C81}"/>
+    <hyperlink ref="I84" r:id="rId4" xr:uid="{D1B57CF3-4B8A-4163-AE81-EB2F92CFF396}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>